--- a/tables/table-5-standard-augmentation-results.xlsx
+++ b/tables/table-5-standard-augmentation-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A45F13FE-C1C3-43C4-B429-25DA537B4649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{A45F13FE-C1C3-43C4-B429-25DA537B4649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{648917A0-7E4C-4EB4-9161-BD5322777A94}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{73D0EFA5-EE9B-4F9F-BFDB-9289CB1225E2}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Table 5: Standard Augmentation Results</t>
   </si>
@@ -33,15 +33,6 @@
     <t>Architecture</t>
   </si>
   <si>
-    <t>Cutmix</t>
-  </si>
-  <si>
-    <t>Standard Augmentations</t>
-  </si>
-  <si>
-    <t>Improvement</t>
-  </si>
-  <si>
     <t>Total Confused Pairs</t>
   </si>
   <si>
@@ -70,13 +61,34 @@
   </si>
   <si>
     <t>1 h 42 min 30 s</t>
+  </si>
+  <si>
+    <t>Cutmix (%)</t>
+  </si>
+  <si>
+    <t>Standard Augmentations (%)</t>
+  </si>
+  <si>
+    <t>Improvement (%)</t>
+  </si>
+  <si>
+    <t>- 0.8</t>
+  </si>
+  <si>
+    <t>+ 1.2</t>
+  </si>
+  <si>
+    <t>- 0.4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,16 +109,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -117,39 +142,58 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -465,120 +509,121 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.140625" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:6" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.98</v>
-      </c>
-      <c r="D3" s="3">
-        <v>-8.0000000000000002E-3</v>
+        <v>4</v>
+      </c>
+      <c r="B3" s="7">
+        <v>98.8</v>
+      </c>
+      <c r="C3" s="7">
+        <v>98</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="E3" s="2">
         <v>5</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.98</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1.2E-2</v>
+        <v>6</v>
+      </c>
+      <c r="B4" s="7">
+        <v>98</v>
+      </c>
+      <c r="C4" s="7">
+        <v>99.2</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="E4" s="2">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.99199999999999999</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="D5" s="3">
-        <v>-4.0000000000000001E-3</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="7">
+        <v>99.2</v>
+      </c>
+      <c r="C5" s="7">
+        <v>98.8</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="E5" s="2">
         <v>3</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0.98</v>
-      </c>
-      <c r="D6" s="5">
-        <v>-8.0000000000000002E-3</v>
-      </c>
-      <c r="E6" s="4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="8">
+        <v>98.8</v>
+      </c>
+      <c r="C6" s="8">
+        <v>98</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>14</v>
+      <c r="F6" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
